--- a/Sprint-1-Login-Module/09-Bug-Reports.xlsx
+++ b/Sprint-1-Login-Module/09-Bug-Reports.xlsx
@@ -1,131 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AJIT KUMAR\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72FB828-195B-4079-AC3F-AC52F128E5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bug Reports" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Reports" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>Bug ID</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Related Test Case</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Steps to Reproduce</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Reported By</t>
-  </si>
-  <si>
-    <t>Reported Date</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>BUG-001</t>
-  </si>
-  <si>
-    <t>Login/Home Dashboard</t>
-  </si>
-  <si>
-    <t>TC_LOGIN_041</t>
-  </si>
-  <si>
-    <t>Welcome message displays untranslated localization key</t>
-  </si>
-  <si>
-    <t>After successful login, the dashboard welcome message contains the text 'labels.text.To' instead of a user-friendly message.</t>
-  </si>
-  <si>
-    <t>1. Open Mifos Login page
-2. Login using valid credentials (mifos/password)
-3. Observe the welcome message on the Home Dashboard</t>
-  </si>
-  <si>
-    <t>Welcome message should display readable text such as 'Welcome mifos to Default!' or an equivalent localized message.</t>
-  </si>
-  <si>
-    <t>Welcome message displays: 'Welcome mifos labels.text.To Default!'</t>
-  </si>
-  <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Ajit Kumar</t>
-  </si>
-  <si>
-    <t>Likely localization (i18n) key not resolved. Needs developer verification.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -144,27 +51,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -452,105 +418,330 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20" style="2" customWidth="1"/>
-    <col min="4" max="8" width="45" style="2" customWidth="1"/>
-    <col min="9" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16" style="2" customWidth="1"/>
-    <col min="14" max="14" width="45" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="2"/>
+    <col width="10" customWidth="1" style="2" min="1" max="1"/>
+    <col width="23" customWidth="1" style="2" min="2" max="2"/>
+    <col width="20" customWidth="1" style="2" min="3" max="3"/>
+    <col width="45" customWidth="1" style="2" min="4" max="8"/>
+    <col width="11" customWidth="1" style="2" min="9" max="10"/>
+    <col width="9" customWidth="1" style="2" min="11" max="11"/>
+    <col width="14" customWidth="1" style="2" min="12" max="12"/>
+    <col width="16" customWidth="1" style="2" min="13" max="13"/>
+    <col width="45" customWidth="1" style="2" min="14" max="14"/>
+    <col width="8.88671875" customWidth="1" style="2" min="15" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Related Test Case</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps to Reproduce</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reported By</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reported Date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>26</v>
+    <row r="2" ht="57.6" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Login/Home Dashboard</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>TC_LOGIN_041</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Welcome message displays untranslated localization key</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>After successful login, the dashboard welcome message contains the text 'labels.text.To' instead of a user-friendly message.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Mifos Login page
+2. Login using valid credentials (mifos/password)
+3. Observe the welcome message on the Home Dashboard</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Welcome message should display readable text such as 'Welcome mifos to Default!' or an equivalent localized message.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Welcome message displays: 'Welcome mifos labels.text.To Default!'</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Ajit Kumar</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Likely localization (i18n) key not resolved. Needs developer verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Username accepts leading spaces</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The Login username field accepts input containing leading spaces.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Leading spaces should be rejected or handled according to the username validation rule.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Username with leading spaces is accepted, causing the test case to fail.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Ajit Kumar</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Source: Sprint 1 Manual Testing – TC_LOGIN_012.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Username accepts trailing spaces</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The Login username field accepts input containing trailing spaces.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Trailing spaces should be rejected or handled according to the username validation rule.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Username with trailing spaces is accepted, causing the test case to fail.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Ajit Kumar</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Source: Sprint 1 Manual Testing – TC_LOGIN_013.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Invalid Server URL requires verification</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The Invalid Server URL scenario failed during manual testing and is marked as requiring verification.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>An invalid Server URL should be rejected or produce the expected validation/configuration behavior.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>The observed behavior requires additional verification before the defect can be formally confirmed.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Pending Verification</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Ajit Kumar</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Source: TC_LOGIN_039. Confirm before assigning final severity/priority and treating it as a confirmed defect.</t>
+        </is>
       </c>
     </row>
   </sheetData>
